--- a/samples/SAMPLE-Platinum-list.xlsx
+++ b/samples/SAMPLE-Platinum-list.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,6 +415,12 @@
       <c r="E1" t="str">
         <v>Platinum Achieved</v>
       </c>
+      <c r="F1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Phone</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +438,12 @@
       <c r="E2" t="str">
         <v>2026-01-20</v>
       </c>
+      <c r="F2" t="str">
+        <v>helene@example.com</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -449,6 +461,12 @@
       <c r="E3" t="str">
         <v>2026-02-11</v>
       </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>905-555-0177</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -466,10 +484,16 @@
       <c r="E4" t="str">
         <v>2026-04-08</v>
       </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/SAMPLE-Platinum-list.xlsx
+++ b/samples/SAMPLE-Platinum-list.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,12 +413,15 @@
         <v>Employer</v>
       </c>
       <c r="E1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="F1" t="str">
         <v>Platinum Achieved</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Email</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Phone</v>
       </c>
     </row>
@@ -436,12 +439,15 @@
         <v>Carrosserie Saint-Laurent</v>
       </c>
       <c r="E2" t="str">
+        <v>Refinish Technician</v>
+      </c>
+      <c r="F2" t="str">
         <v>2026-01-20</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>helene@example.com</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v/>
       </c>
     </row>
@@ -459,12 +465,15 @@
         <v>Maple Leaf Collision Ltd.</v>
       </c>
       <c r="E3" t="str">
+        <v>Steel Structural Technician</v>
+      </c>
+      <c r="F3" t="str">
         <v>2026-02-11</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v/>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>905-555-0177</v>
       </c>
     </row>
@@ -482,18 +491,21 @@
         <v>Prairie Auto Body</v>
       </c>
       <c r="E4" t="str">
+        <v>Estimator</v>
+      </c>
+      <c r="F4" t="str">
         <v>2026-04-08</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v/>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>